--- a/data/povertybenelux.xlsx
+++ b/data/povertybenelux.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\GitHub\happiness\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{522B3864-E9D6-4ACA-A9BA-DCAABA08CAE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD18D8B3-2C1F-4CA2-97A9-531B94ACC31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{BA9ABFDD-ED0F-4735-B979-7130B82A3358}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>Belgium</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>18.1%</t>
+  </si>
+  <si>
+    <t>Country</t>
   </si>
 </sst>
 </file>
@@ -509,6 +512,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="B1">
         <v>2014</v>
       </c>
@@ -675,6 +681,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D25CF0B9B9713944843C6634AD94B5CD" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="6fc06c35c9fb9ff8495a9005fb1aa923">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f4a0f2c8-0374-43bc-b7f6-d31395797ed2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffa17790aa560c96c4a002fed6eed5a2" ns3:_="">
     <xsd:import namespace="f4a0f2c8-0374-43bc-b7f6-d31395797ed2"/>
@@ -818,15 +833,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -834,6 +840,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7FD4C50-C95D-4F63-99A2-1A1410426D88}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CEE2B22-C51B-4510-B78A-A663C5308629}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -851,14 +865,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7FD4C50-C95D-4F63-99A2-1A1410426D88}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9289760-C5DA-4823-9A23-E0833EE59D75}">
   <ds:schemaRefs>

--- a/data/povertybenelux.xlsx
+++ b/data/povertybenelux.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luukn\Documents\GitHub\happiness\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD18D8B3-2C1F-4CA2-97A9-531B94ACC31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3350002F-72DF-4F41-8505-2432BCB555C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{BA9ABFDD-ED0F-4735-B979-7130B82A3358}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>Belgium</t>
   </si>
@@ -107,12 +107,6 @@
     <t>13.0%</t>
   </si>
   <si>
-    <t>16.9%</t>
-  </si>
-  <si>
-    <t>15.6%</t>
-  </si>
-  <si>
     <t>17.5%</t>
   </si>
   <si>
@@ -123,6 +117,21 @@
   </si>
   <si>
     <t>Country</t>
+  </si>
+  <si>
+    <t>15.3%</t>
+  </si>
+  <si>
+    <t>15.8%</t>
+  </si>
+  <si>
+    <t>16.7%</t>
+  </si>
+  <si>
+    <t>17.4%</t>
+  </si>
+  <si>
+    <t>18.8%</t>
   </si>
 </sst>
 </file>
@@ -513,7 +522,7 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B1">
         <v>2014</v>
@@ -584,13 +593,13 @@
         <v>10</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -631,7 +640,7 @@
         <v>20</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -642,34 +651,34 @@
         <v>3</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
         <v>3</v>
       </c>
       <c r="F4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
         <v>25</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" t="s">
         <v>25</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" t="s">
-        <v>26</v>
-      </c>
-      <c r="J4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
       </c>
       <c r="M4" t="s">
         <v>4</v>
@@ -681,15 +690,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D25CF0B9B9713944843C6634AD94B5CD" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="6fc06c35c9fb9ff8495a9005fb1aa923">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f4a0f2c8-0374-43bc-b7f6-d31395797ed2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ffa17790aa560c96c4a002fed6eed5a2" ns3:_="">
     <xsd:import namespace="f4a0f2c8-0374-43bc-b7f6-d31395797ed2"/>
@@ -833,6 +833,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -840,14 +849,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7FD4C50-C95D-4F63-99A2-1A1410426D88}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8CEE2B22-C51B-4510-B78A-A663C5308629}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -865,6 +866,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7FD4C50-C95D-4F63-99A2-1A1410426D88}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B9289760-C5DA-4823-9A23-E0833EE59D75}">
   <ds:schemaRefs>
